--- a/catch_per_trap.xlsx
+++ b/catch_per_trap.xlsx
@@ -367,7 +367,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -417,7 +417,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D2">
@@ -457,7 +457,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D3">
@@ -497,7 +497,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D4">
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D5">
@@ -577,22 +577,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>norrbotten_5</t>
+          <t>västernorrland_1</t>
         </is>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -617,22 +617,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>norrbotten_6</t>
+          <t>västernorrland_2</t>
         </is>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -657,22 +657,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>norrbotten_7</t>
+          <t>västernorrland_3</t>
         </is>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -697,22 +697,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>norrbotten_8</t>
+          <t>västernorrland_4</t>
         </is>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>5</v>
-      </c>
-      <c r="J9">
-        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -737,22 +737,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>norrbotten_9</t>
+          <t>västernorrland_5</t>
         </is>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -777,22 +777,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>norrbotten_10</t>
+          <t>västernorrland_6</t>
         </is>
       </c>
       <c r="G11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -817,22 +817,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12">
-        <v>6069</v>
+        <v>5463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>norrbotten_11</t>
+          <t>västernorrland_7</t>
         </is>
       </c>
       <c r="G12">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -852,38 +852,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>norrbotten_12</t>
+          <t>västernorrland_1</t>
         </is>
       </c>
       <c r="G13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J13">
-        <v>65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
@@ -892,38 +892,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>norrbotten_13</t>
+          <t>västernorrland_2</t>
         </is>
       </c>
       <c r="G14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J14">
-        <v>65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -932,38 +932,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>norrbotten_14</t>
+          <t>västernorrland_3</t>
         </is>
       </c>
       <c r="G15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J15">
-        <v>65</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -972,38 +972,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D16">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>norrbotten_15</t>
+          <t>västernorrland_4</t>
         </is>
       </c>
       <c r="G16">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J16">
-        <v>65</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -1012,38 +1012,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>norrbotten_16</t>
+          <t>västernorrland_5</t>
         </is>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J17">
-        <v>65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
@@ -1052,38 +1052,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18">
-        <v>6069</v>
+        <v>5362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>norrbotten_17</t>
+          <t>västernorrland_6</t>
         </is>
       </c>
       <c r="G18">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J18">
-        <v>65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
@@ -1092,38 +1092,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>6069</v>
+        <v>5463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>norrbotten_18</t>
+          <t>västernorrland_7</t>
         </is>
       </c>
       <c r="G19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J19">
-        <v>65</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="20">
@@ -1132,38 +1132,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D20">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20">
-        <v>6068</v>
+        <v>5463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>norrbotten_1</t>
+          <t>västernorrland_7</t>
         </is>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I20">
-        <v>1.845833333333333</v>
+        <v>0.25</v>
       </c>
       <c r="J20">
-        <v>3.691666666666666</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="21">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D21">
         <v>31</v>
       </c>
       <c r="E21">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>norrbotten_5</t>
+          <t>norrbotten_2</t>
         </is>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I21">
-        <v>1.845833333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="J21">
-        <v>3.691666666666666</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
@@ -1217,18 +1217,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D22">
         <v>31</v>
       </c>
       <c r="E22">
-        <v>6069</v>
+        <v>6067</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>norrbotten_6</t>
+          <t>norrbotten_3</t>
         </is>
       </c>
       <c r="G22">
@@ -1236,14 +1236,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I22">
-        <v>1.845833333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="J22">
-        <v>3.691666666666666</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -1257,33 +1257,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D23">
         <v>31</v>
       </c>
       <c r="E23">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>norrbotten_7</t>
+          <t>norrbotten_4</t>
         </is>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I23">
-        <v>1.845833333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="J23">
-        <v>18.45833333333333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1297,33 +1297,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D24">
         <v>31</v>
       </c>
       <c r="E24">
-        <v>6069</v>
+        <v>5967</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>norrbotten_8</t>
+          <t>norrbotten_19</t>
         </is>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I24">
-        <v>1.845833333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="J24">
-        <v>18.45833333333333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D25">
         <v>31</v>
       </c>
       <c r="E25">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>norrbotten_9</t>
+          <t>norrbotten_2</t>
         </is>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="I25">
-        <v>1.845833333333333</v>
+        <v>0.875</v>
       </c>
       <c r="J25">
-        <v>18.45833333333333</v>
+        <v>4.375</v>
       </c>
     </row>
     <row r="26">
@@ -1372,27 +1372,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D26">
         <v>31</v>
       </c>
       <c r="E26">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>norrbotten_10</t>
+          <t>norrbotten_4</t>
         </is>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="I26">
-        <v>1.845833333333333</v>
+        <v>0.875</v>
       </c>
       <c r="J26">
-        <v>18.45833333333333</v>
+        <v>16.625</v>
       </c>
     </row>
     <row r="27">
@@ -1412,27 +1412,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D27">
         <v>31</v>
       </c>
       <c r="E27">
-        <v>6069</v>
+        <v>5967</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>norrbotten_11</t>
+          <t>norrbotten_19</t>
         </is>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="I27">
-        <v>1.845833333333333</v>
+        <v>0.875</v>
       </c>
       <c r="J27">
-        <v>18.45833333333333</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="28">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D28">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>norrbotten_12</t>
+          <t>norrbotten_5</t>
         </is>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I28">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D29">
@@ -1508,22 +1508,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>norrbotten_13</t>
+          <t>norrbotten_6</t>
         </is>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I29">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D30">
@@ -1548,22 +1548,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>norrbotten_14</t>
+          <t>norrbotten_7</t>
         </is>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I30">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D31">
@@ -1588,22 +1588,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>norrbotten_15</t>
+          <t>norrbotten_8</t>
         </is>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I31">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D32">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>norrbotten_16</t>
+          <t>norrbotten_9</t>
         </is>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I32">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D33">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>norrbotten_17</t>
+          <t>norrbotten_10</t>
         </is>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I33">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D34">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>norrbotten_18</t>
+          <t>norrbotten_11</t>
         </is>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I34">
-        <v>1.845833333333333</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>18.45833333333333</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D35">
@@ -1748,22 +1748,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>norrbotten_7</t>
+          <t>norrbotten_12</t>
         </is>
       </c>
       <c r="G35">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I35">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D36">
@@ -1788,22 +1788,22 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>norrbotten_8</t>
+          <t>norrbotten_13</t>
         </is>
       </c>
       <c r="G36">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I36">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D37">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>norrbotten_9</t>
+          <t>norrbotten_14</t>
         </is>
       </c>
       <c r="G37">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I37">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D38">
@@ -1868,22 +1868,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>norrbotten_10</t>
+          <t>norrbotten_15</t>
         </is>
       </c>
       <c r="G38">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I38">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D39">
@@ -1908,22 +1908,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>norrbotten_11</t>
+          <t>norrbotten_16</t>
         </is>
       </c>
       <c r="G39">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I39">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D40">
@@ -1948,22 +1948,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>norrbotten_12</t>
+          <t>norrbotten_17</t>
         </is>
       </c>
       <c r="G40">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I40">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D41">
@@ -1988,22 +1988,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>norrbotten_13</t>
+          <t>norrbotten_18</t>
         </is>
       </c>
       <c r="G41">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I41">
-        <v>0.375</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>9.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
@@ -2012,38 +2012,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D42">
         <v>31</v>
       </c>
       <c r="E42">
-        <v>6069</v>
+        <v>6068</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>norrbotten_14</t>
+          <t>norrbotten_1</t>
         </is>
       </c>
       <c r="G42">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I42">
-        <v>0.375</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J42">
-        <v>9.75</v>
+        <v>3.691666666666666</v>
       </c>
     </row>
     <row r="43">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D43">
@@ -2068,22 +2068,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>norrbotten_15</t>
+          <t>norrbotten_5</t>
         </is>
       </c>
       <c r="G43">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I43">
-        <v>0.375</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J43">
-        <v>9.75</v>
+        <v>3.691666666666666</v>
       </c>
     </row>
     <row r="44">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D44">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>norrbotten_16</t>
+          <t>norrbotten_6</t>
         </is>
       </c>
       <c r="G44">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I44">
-        <v>0.375</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J44">
-        <v>9.75</v>
+        <v>3.691666666666666</v>
       </c>
     </row>
     <row r="45">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D45">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>norrbotten_17</t>
+          <t>norrbotten_7</t>
         </is>
       </c>
       <c r="G45">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I45">
-        <v>0.375</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J45">
-        <v>9.75</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="46">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D46">
@@ -2188,22 +2188,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>norrbotten_18</t>
+          <t>norrbotten_8</t>
         </is>
       </c>
       <c r="G46">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I46">
-        <v>0.375</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J46">
-        <v>9.75</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="47">
@@ -2217,33 +2217,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D47">
         <v>31</v>
       </c>
       <c r="E47">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>norrbotten_2</t>
+          <t>norrbotten_9</t>
         </is>
       </c>
       <c r="G47">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I47">
-        <v>2.266666666666666</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J47">
-        <v>67.99999999999997</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="48">
@@ -2257,33 +2257,33 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D48">
         <v>31</v>
       </c>
       <c r="E48">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>norrbotten_3</t>
+          <t>norrbotten_10</t>
         </is>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I48">
-        <v>2.266666666666666</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J48">
-        <v>4.533333333333331</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="49">
@@ -2297,33 +2297,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D49">
         <v>31</v>
       </c>
       <c r="E49">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>norrbotten_4</t>
+          <t>norrbotten_11</t>
         </is>
       </c>
       <c r="G49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I49">
-        <v>2.266666666666666</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J49">
-        <v>20.39999999999999</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="50">
@@ -2337,33 +2337,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D50">
         <v>31</v>
       </c>
       <c r="E50">
-        <v>5967</v>
+        <v>6069</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>norrbotten_19</t>
+          <t>norrbotten_12</t>
         </is>
       </c>
       <c r="G50">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I50">
-        <v>2.266666666666666</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J50">
-        <v>20.39999999999999</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="51">
@@ -2372,27 +2372,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D51">
         <v>31</v>
       </c>
       <c r="E51">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>norrbotten_2</t>
+          <t>norrbotten_13</t>
         </is>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="I51">
-        <v>0.8583333333333332</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J51">
-        <v>4.291666666666666</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="52">
@@ -2412,27 +2412,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D52">
         <v>31</v>
       </c>
       <c r="E52">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>norrbotten_4</t>
+          <t>norrbotten_14</t>
         </is>
       </c>
       <c r="G52">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="I52">
-        <v>0.8583333333333332</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J52">
-        <v>16.30833333333333</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="53">
@@ -2452,27 +2452,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D53">
         <v>31</v>
       </c>
       <c r="E53">
-        <v>5967</v>
+        <v>6069</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>norrbotten_19</t>
+          <t>norrbotten_15</t>
         </is>
       </c>
       <c r="G53">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="I53">
-        <v>0.8583333333333332</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J53">
-        <v>22.31666666666666</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="54">
@@ -2492,23 +2492,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D54">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E54">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>västernorrland_1</t>
+          <t>norrbotten_16</t>
         </is>
       </c>
       <c r="G54">
@@ -2516,14 +2516,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J54">
-        <v>10</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="55">
@@ -2532,23 +2532,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E55">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>västernorrland_2</t>
+          <t>norrbotten_17</t>
         </is>
       </c>
       <c r="G55">
@@ -2556,14 +2556,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="56">
@@ -2572,38 +2572,38 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D56">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E56">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>västernorrland_3</t>
+          <t>norrbotten_18</t>
         </is>
       </c>
       <c r="G56">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>1.845833333333333</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>18.45833333333333</v>
       </c>
     </row>
     <row r="57">
@@ -2612,38 +2612,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D57">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E57">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>västernorrland_4</t>
+          <t>norrbotten_7</t>
         </is>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="58">
@@ -2652,38 +2652,38 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D58">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E58">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>västernorrland_5</t>
+          <t>norrbotten_8</t>
         </is>
       </c>
       <c r="G58">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="J58">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="59">
@@ -2692,38 +2692,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D59">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E59">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>västernorrland_6</t>
+          <t>norrbotten_9</t>
         </is>
       </c>
       <c r="G59">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="J59">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="60">
@@ -2732,38 +2732,38 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D60">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E60">
-        <v>5463</v>
+        <v>6069</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>västernorrland_7</t>
+          <t>norrbotten_10</t>
         </is>
       </c>
       <c r="G60">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="J60">
-        <v>29</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="61">
@@ -2772,38 +2772,38 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D61">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E61">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>västernorrland_1</t>
+          <t>norrbotten_11</t>
         </is>
       </c>
       <c r="G61">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I61">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J61">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="62">
@@ -2812,38 +2812,38 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D62">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E62">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>västernorrland_2</t>
+          <t>norrbotten_12</t>
         </is>
       </c>
       <c r="G62">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I62">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J62">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="63">
@@ -2852,38 +2852,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D63">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E63">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>västernorrland_3</t>
+          <t>norrbotten_13</t>
         </is>
       </c>
       <c r="G63">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I63">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J63">
-        <v>3.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="64">
@@ -2892,38 +2892,38 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D64">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E64">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>västernorrland_4</t>
+          <t>norrbotten_14</t>
         </is>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I64">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J64">
-        <v>2.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="65">
@@ -2932,38 +2932,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D65">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E65">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>västernorrland_5</t>
+          <t>norrbotten_15</t>
         </is>
       </c>
       <c r="G65">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I65">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J65">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="66">
@@ -2972,38 +2972,38 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D66">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E66">
-        <v>5362</v>
+        <v>6069</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>västernorrland_6</t>
+          <t>norrbotten_16</t>
         </is>
       </c>
       <c r="G66">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I66">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J66">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="67">
@@ -3012,38 +3012,38 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D67">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E67">
-        <v>5463</v>
+        <v>6069</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>västernorrland_7</t>
+          <t>norrbotten_17</t>
         </is>
       </c>
       <c r="G67">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I67">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="J67">
-        <v>15.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="68">
@@ -3057,22 +3057,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D68">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E68">
-        <v>5463</v>
+        <v>6069</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>västernorrland_7</t>
+          <t>norrbotten_18</t>
         </is>
       </c>
       <c r="G68">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="I68">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="J68">
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="69">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D69">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D70">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D71">
@@ -3217,22 +3217,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D72">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E72">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>norrbotten_21</t>
+          <t>västernorrland_8</t>
         </is>
       </c>
       <c r="G72">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="I72">
-        <v>4.940000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J72">
-        <v>93.86000000000003</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -3257,22 +3257,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D73">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E73">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>norrbotten_22</t>
+          <t>västernorrland_9</t>
         </is>
       </c>
       <c r="G73">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="I73">
-        <v>4.940000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J73">
-        <v>93.86000000000003</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -3297,22 +3297,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D74">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E74">
-        <v>6069</v>
+        <v>5463</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>norrbotten_24</t>
+          <t>västernorrland_10</t>
         </is>
       </c>
       <c r="G74">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="I74">
-        <v>4.940000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J74">
-        <v>64.22000000000001</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="75">
@@ -3332,38 +3332,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D75">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E75">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>norrbotten_26</t>
+          <t>västernorrland_8</t>
         </is>
       </c>
       <c r="G75">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I75">
-        <v>4.940000000000001</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J75">
-        <v>64.22000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -3372,38 +3372,38 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D76">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E76">
-        <v>6069</v>
+        <v>5564</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>norrbotten_27</t>
+          <t>västernorrland_9</t>
         </is>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I76">
-        <v>4.940000000000001</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J76">
-        <v>29.64000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -3412,38 +3412,38 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D77">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E77">
-        <v>6069</v>
+        <v>5463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>norrbotten_28</t>
+          <t>västernorrland_10</t>
         </is>
       </c>
       <c r="G77">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I77">
-        <v>4.940000000000001</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J77">
-        <v>29.64000000000001</v>
+        <v>20.66666666666666</v>
       </c>
     </row>
     <row r="78">
@@ -3452,38 +3452,38 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D78">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E78">
-        <v>6068</v>
+        <v>5463</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>norrbotten_20</t>
+          <t>västernorrland_10</t>
         </is>
       </c>
       <c r="G78">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I78">
-        <v>1.7375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J78">
-        <v>50.3875</v>
+        <v>10.33333333333333</v>
       </c>
     </row>
     <row r="79">
@@ -3497,33 +3497,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D79">
         <v>31</v>
       </c>
       <c r="E79">
-        <v>6069</v>
+        <v>6067</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>norrbotten_21</t>
+          <t>norrbotten_23</t>
         </is>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I79">
-        <v>1.7375</v>
+        <v>3</v>
       </c>
       <c r="J79">
-        <v>1.7375</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
@@ -3537,33 +3537,33 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D80">
         <v>31</v>
       </c>
       <c r="E80">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>norrbotten_22</t>
+          <t>norrbotten_29</t>
         </is>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I80">
-        <v>1.7375</v>
+        <v>3</v>
       </c>
       <c r="J80">
-        <v>1.7375</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81">
@@ -3577,33 +3577,33 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D81">
         <v>31</v>
       </c>
       <c r="E81">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>norrbotten_24</t>
+          <t>norrbotten_30</t>
         </is>
       </c>
       <c r="G81">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I81">
-        <v>1.7375</v>
+        <v>3</v>
       </c>
       <c r="J81">
-        <v>53.8625</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82">
@@ -3612,27 +3612,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D82">
         <v>31</v>
       </c>
       <c r="E82">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>norrbotten_25</t>
+          <t>norrbotten_23</t>
         </is>
       </c>
       <c r="G82">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="I82">
-        <v>1.7375</v>
+        <v>1.25</v>
       </c>
       <c r="J82">
-        <v>19.1125</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="83">
@@ -3652,27 +3652,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D83">
         <v>31</v>
       </c>
       <c r="E83">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>norrbotten_26</t>
+          <t>norrbotten_29</t>
         </is>
       </c>
       <c r="G83">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="I83">
-        <v>1.7375</v>
+        <v>1.25</v>
       </c>
       <c r="J83">
-        <v>3.475</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
@@ -3697,33 +3697,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D84">
         <v>31</v>
       </c>
       <c r="E84">
-        <v>6068</v>
+        <v>5966</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>norrbotten_20</t>
+          <t>norrbotten_30</t>
         </is>
       </c>
       <c r="G84">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I84">
-        <v>0.6268253968253968</v>
+        <v>1.25</v>
       </c>
       <c r="J84">
-        <v>9.402380952380952</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D85">
@@ -3748,22 +3748,22 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>norrbotten_24</t>
+          <t>norrbotten_21</t>
         </is>
       </c>
       <c r="G85">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I85">
-        <v>0.6268253968253968</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="J85">
-        <v>9.402380952380952</v>
+        <v>93.86000000000003</v>
       </c>
     </row>
     <row r="86">
@@ -3772,38 +3772,38 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D86">
         <v>31</v>
       </c>
       <c r="E86">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>norrbotten_25</t>
+          <t>norrbotten_22</t>
         </is>
       </c>
       <c r="G86">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I86">
-        <v>0.6268253968253968</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="J86">
-        <v>19.4315873015873</v>
+        <v>93.86000000000003</v>
       </c>
     </row>
     <row r="87">
@@ -3812,27 +3812,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D87">
         <v>31</v>
       </c>
       <c r="E87">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>norrbotten_23</t>
+          <t>norrbotten_24</t>
         </is>
       </c>
       <c r="G87">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="I87">
-        <v>3</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="J87">
-        <v>33</v>
+        <v>64.22000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3852,27 +3852,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D88">
         <v>31</v>
       </c>
       <c r="E88">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>norrbotten_29</t>
+          <t>norrbotten_26</t>
         </is>
       </c>
       <c r="G88">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="J88">
-        <v>33</v>
+        <v>64.22000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3892,27 +3892,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D89">
         <v>31</v>
       </c>
       <c r="E89">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>norrbotten_30</t>
+          <t>norrbotten_27</t>
         </is>
       </c>
       <c r="G89">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="I89">
-        <v>3</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="J89">
-        <v>90</v>
+        <v>29.64000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -3932,38 +3932,38 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D90">
         <v>31</v>
       </c>
       <c r="E90">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>norrbotten_23</t>
+          <t>norrbotten_28</t>
         </is>
       </c>
       <c r="G90">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I90">
-        <v>1.25</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="J90">
-        <v>28.75</v>
+        <v>29.64000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -3972,27 +3972,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D91">
         <v>31</v>
       </c>
       <c r="E91">
-        <v>5966</v>
+        <v>6068</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>norrbotten_29</t>
+          <t>norrbotten_20</t>
         </is>
       </c>
       <c r="G91">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="I91">
-        <v>1.25</v>
+        <v>1.7375</v>
       </c>
       <c r="J91">
-        <v>25</v>
+        <v>50.3875</v>
       </c>
     </row>
     <row r="92">
@@ -4012,27 +4012,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D92">
         <v>31</v>
       </c>
       <c r="E92">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>norrbotten_30</t>
+          <t>norrbotten_21</t>
         </is>
       </c>
       <c r="G92">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="I92">
-        <v>1.25</v>
+        <v>1.7375</v>
       </c>
       <c r="J92">
-        <v>25</v>
+        <v>1.7375</v>
       </c>
     </row>
     <row r="93">
@@ -4052,38 +4052,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D93">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>västernorrland_8</t>
+          <t>norrbotten_22</t>
         </is>
       </c>
       <c r="G93">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I93">
-        <v>1.5</v>
+        <v>1.7375</v>
       </c>
       <c r="J93">
-        <v>15</v>
+        <v>1.7375</v>
       </c>
     </row>
     <row r="94">
@@ -4092,38 +4092,38 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D94">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>västernorrland_9</t>
+          <t>norrbotten_24</t>
         </is>
       </c>
       <c r="G94">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I94">
-        <v>1.5</v>
+        <v>1.7375</v>
       </c>
       <c r="J94">
-        <v>15</v>
+        <v>53.8625</v>
       </c>
     </row>
     <row r="95">
@@ -4132,38 +4132,38 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D95">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E95">
-        <v>5463</v>
+        <v>6068</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>västernorrland_10</t>
+          <t>norrbotten_25</t>
         </is>
       </c>
       <c r="G95">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I95">
-        <v>1.5</v>
+        <v>1.7375</v>
       </c>
       <c r="J95">
-        <v>43.5</v>
+        <v>19.1125</v>
       </c>
     </row>
     <row r="96">
@@ -4177,22 +4177,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D96">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E96">
-        <v>5564</v>
+        <v>6069</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>västernorrland_8</t>
+          <t>norrbotten_26</t>
         </is>
       </c>
       <c r="G96">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="I96">
-        <v>0.6666666666666666</v>
+        <v>1.7375</v>
       </c>
       <c r="J96">
-        <v>10</v>
+        <v>3.475</v>
       </c>
     </row>
     <row r="97">
@@ -4212,23 +4212,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D97">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E97">
-        <v>5564</v>
+        <v>6068</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>västernorrland_9</t>
+          <t>norrbotten_20</t>
         </is>
       </c>
       <c r="G97">
@@ -4236,14 +4236,14 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I97">
-        <v>0.6666666666666666</v>
+        <v>0.6268253968253968</v>
       </c>
       <c r="J97">
-        <v>10</v>
+        <v>9.402380952380952</v>
       </c>
     </row>
     <row r="98">
@@ -4252,38 +4252,38 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D98">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E98">
-        <v>5463</v>
+        <v>6069</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>västernorrland_10</t>
+          <t>norrbotten_24</t>
         </is>
       </c>
       <c r="G98">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I98">
-        <v>0.6666666666666666</v>
+        <v>0.6268253968253968</v>
       </c>
       <c r="J98">
-        <v>20.66666666666666</v>
+        <v>9.402380952380952</v>
       </c>
     </row>
     <row r="99">
@@ -4297,18 +4297,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sundsvall</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D99">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E99">
-        <v>5463</v>
+        <v>6068</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>västernorrland_10</t>
+          <t>norrbotten_25</t>
         </is>
       </c>
       <c r="G99">
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.3333333333333333</v>
+        <v>0.6268253968253968</v>
       </c>
       <c r="J99">
-        <v>10.33333333333333</v>
+        <v>19.4315873015873</v>
       </c>
     </row>
     <row r="100">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D100">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D101">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>gavle</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="D102">
@@ -4452,27 +4452,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D103">
         <v>31</v>
       </c>
       <c r="E103">
-        <v>6069</v>
+        <v>6067</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>norrbotten_32</t>
+          <t>norrbotten_31</t>
         </is>
       </c>
       <c r="G103">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="I103">
-        <v>2.5</v>
+        <v>1.716666666666666</v>
       </c>
       <c r="J103">
-        <v>32.5</v>
+        <v>51.49999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -4492,27 +4492,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D104">
         <v>31</v>
       </c>
       <c r="E104">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>norrbotten_33</t>
+          <t>norrbotten_34</t>
         </is>
       </c>
       <c r="G104">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="I104">
-        <v>2.5</v>
+        <v>1.716666666666666</v>
       </c>
       <c r="J104">
-        <v>32.5</v>
+        <v>46.34999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -4532,27 +4532,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D105">
         <v>31</v>
       </c>
       <c r="E105">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>norrbotten_38</t>
+          <t>norrbotten_36</t>
         </is>
       </c>
       <c r="G105">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="I105">
-        <v>2.5</v>
+        <v>1.716666666666666</v>
       </c>
       <c r="J105">
-        <v>25</v>
+        <v>51.49999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -4572,27 +4572,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D106">
         <v>31</v>
       </c>
       <c r="E106">
-        <v>6069</v>
+        <v>6067</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>norrbotten_40</t>
+          <t>norrbotten_37</t>
         </is>
       </c>
       <c r="G106">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="I106">
-        <v>2.5</v>
+        <v>1.716666666666666</v>
       </c>
       <c r="J106">
-        <v>32.5</v>
+        <v>34.33333333333333</v>
       </c>
     </row>
     <row r="107">
@@ -4612,27 +4612,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D107">
         <v>31</v>
       </c>
       <c r="E107">
-        <v>6069</v>
+        <v>6067</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>norrbotten_32</t>
+          <t>norrbotten_31</t>
         </is>
       </c>
       <c r="G107">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>0.9833333333333331</v>
       </c>
       <c r="J107">
-        <v>31</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="108">
@@ -4652,27 +4652,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D108">
         <v>31</v>
       </c>
       <c r="E108">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>norrbotten_33</t>
+          <t>norrbotten_34</t>
         </is>
       </c>
       <c r="G108">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>0.9833333333333331</v>
       </c>
       <c r="J108">
-        <v>31</v>
+        <v>21.63333333333333</v>
       </c>
     </row>
     <row r="109">
@@ -4692,27 +4692,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D109">
         <v>31</v>
       </c>
       <c r="E109">
-        <v>6068</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>norrbotten_35</t>
+          <t>norrbotten_36</t>
         </is>
       </c>
       <c r="G109">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0.9833333333333331</v>
       </c>
       <c r="J109">
-        <v>30</v>
+        <v>18.68333333333333</v>
       </c>
     </row>
     <row r="110">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D110">
@@ -4748,22 +4748,22 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>norrbotten_38</t>
+          <t>norrbotten_32</t>
         </is>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="111">
@@ -4772,38 +4772,38 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D111">
         <v>31</v>
       </c>
       <c r="E111">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>norrbotten_39</t>
+          <t>norrbotten_33</t>
         </is>
       </c>
       <c r="G111">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J111">
-        <v>8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="112">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D112">
@@ -4828,22 +4828,22 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>norrbotten_40</t>
+          <t>norrbotten_38</t>
         </is>
       </c>
       <c r="G112">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I112">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J112">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D113">
@@ -4868,22 +4868,22 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>norrbotten_32</t>
+          <t>norrbotten_40</t>
         </is>
       </c>
       <c r="G113">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I113">
-        <v>0.2896103896103896</v>
+        <v>2.5</v>
       </c>
       <c r="J113">
-        <v>4.344155844155844</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="114">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D114">
@@ -4908,22 +4908,22 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>norrbotten_33</t>
+          <t>norrbotten_32</t>
         </is>
       </c>
       <c r="G114">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I114">
-        <v>0.2896103896103896</v>
+        <v>1</v>
       </c>
       <c r="J114">
-        <v>4.344155844155844</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115">
@@ -4932,38 +4932,38 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D115">
         <v>31</v>
       </c>
       <c r="E115">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>norrbotten_35</t>
+          <t>norrbotten_33</t>
         </is>
       </c>
       <c r="G115">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I115">
-        <v>0.2896103896103896</v>
+        <v>1</v>
       </c>
       <c r="J115">
-        <v>4.344155844155844</v>
+        <v>31</v>
       </c>
     </row>
     <row r="116">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D116">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>norrbotten_39</t>
+          <t>norrbotten_35</t>
         </is>
       </c>
       <c r="G116">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I116">
-        <v>0.2896103896103896</v>
+        <v>1</v>
       </c>
       <c r="J116">
-        <v>6.371428571428571</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117">
@@ -5017,33 +5017,33 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D117">
         <v>31</v>
       </c>
       <c r="E117">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>norrbotten_31</t>
+          <t>norrbotten_38</t>
         </is>
       </c>
       <c r="G117">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I117">
-        <v>1.716666666666666</v>
+        <v>1</v>
       </c>
       <c r="J117">
-        <v>51.49999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -5057,33 +5057,33 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D118">
         <v>31</v>
       </c>
       <c r="E118">
-        <v>5966</v>
+        <v>6068</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>norrbotten_34</t>
+          <t>norrbotten_39</t>
         </is>
       </c>
       <c r="G118">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I118">
-        <v>1.716666666666666</v>
+        <v>1</v>
       </c>
       <c r="J118">
-        <v>46.34999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -5097,33 +5097,33 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D119">
         <v>31</v>
       </c>
       <c r="E119">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>norrbotten_36</t>
+          <t>norrbotten_40</t>
         </is>
       </c>
       <c r="G119">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I119">
-        <v>1.716666666666666</v>
+        <v>1</v>
       </c>
       <c r="J119">
-        <v>51.49999999999999</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
@@ -5132,38 +5132,38 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D120">
         <v>31</v>
       </c>
       <c r="E120">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>norrbotten_37</t>
+          <t>norrbotten_32</t>
         </is>
       </c>
       <c r="G120">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I120">
-        <v>1.716666666666666</v>
+        <v>0.306818181818182</v>
       </c>
       <c r="J120">
-        <v>34.33333333333333</v>
+        <v>4.60227272727273</v>
       </c>
     </row>
     <row r="121">
@@ -5177,18 +5177,18 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D121">
         <v>31</v>
       </c>
       <c r="E121">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>norrbotten_31</t>
+          <t>norrbotten_33</t>
         </is>
       </c>
       <c r="G121">
@@ -5196,14 +5196,14 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I121">
-        <v>0.9833333333333331</v>
+        <v>0.306818181818182</v>
       </c>
       <c r="J121">
-        <v>14.75</v>
+        <v>4.60227272727273</v>
       </c>
     </row>
     <row r="122">
@@ -5217,33 +5217,33 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D122">
         <v>31</v>
       </c>
       <c r="E122">
-        <v>5966</v>
+        <v>6068</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>norrbotten_34</t>
+          <t>norrbotten_35</t>
         </is>
       </c>
       <c r="G122">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I122">
-        <v>0.9833333333333331</v>
+        <v>0.306818181818182</v>
       </c>
       <c r="J122">
-        <v>21.63333333333333</v>
+        <v>4.60227272727273</v>
       </c>
     </row>
     <row r="123">
@@ -5257,33 +5257,33 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D123">
         <v>31</v>
       </c>
       <c r="E123">
-        <v>5966</v>
+        <v>6068</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>norrbotten_36</t>
+          <t>norrbotten_39</t>
         </is>
       </c>
       <c r="G123">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I123">
-        <v>0.9833333333333331</v>
+        <v>0.306818181818182</v>
       </c>
       <c r="J123">
-        <v>18.68333333333333</v>
+        <v>6.750000000000004</v>
       </c>
     </row>
     <row r="124">
@@ -5292,27 +5292,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D124">
         <v>31</v>
       </c>
       <c r="E124">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>norrbotten_41</t>
+          <t>norrbotten_43</t>
         </is>
       </c>
       <c r="G124">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5320,10 +5320,10 @@
         </is>
       </c>
       <c r="I124">
-        <v>2.192380952380952</v>
+        <v>1.419047619047619</v>
       </c>
       <c r="J124">
-        <v>28.50095238095238</v>
+        <v>41.15238095238094</v>
       </c>
     </row>
     <row r="125">
@@ -5332,27 +5332,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D125">
         <v>31</v>
       </c>
       <c r="E125">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>norrbotten_42</t>
+          <t>norrbotten_44</t>
         </is>
       </c>
       <c r="G125">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="I125">
-        <v>2.192380952380952</v>
+        <v>1.419047619047619</v>
       </c>
       <c r="J125">
-        <v>28.50095238095238</v>
+        <v>42.57142857142857</v>
       </c>
     </row>
     <row r="126">
@@ -5372,38 +5372,38 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D126">
         <v>31</v>
       </c>
       <c r="E126">
-        <v>6069</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>norrbotten_45</t>
+          <t>norrbotten_43</t>
         </is>
       </c>
       <c r="G126">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I126">
-        <v>2.192380952380952</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J126">
-        <v>28.50095238095238</v>
+        <v>12.66666666666667</v>
       </c>
     </row>
     <row r="127">
@@ -5412,38 +5412,38 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Luleå</t>
         </is>
       </c>
       <c r="D127">
         <v>31</v>
       </c>
       <c r="E127">
-        <v>6068</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>norrbotten_46</t>
+          <t>norrbotten_44</t>
         </is>
       </c>
       <c r="G127">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I127">
-        <v>2.192380952380952</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J127">
-        <v>28.50095238095238</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D128">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>norrbotten_47</t>
+          <t>norrbotten_41</t>
         </is>
       </c>
       <c r="G128">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D129">
@@ -5508,22 +5508,22 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>norrbotten_41</t>
+          <t>norrbotten_42</t>
         </is>
       </c>
       <c r="G129">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I129">
-        <v>0.6727272727272724</v>
+        <v>2.192380952380952</v>
       </c>
       <c r="J129">
-        <v>20.85454545454544</v>
+        <v>28.50095238095238</v>
       </c>
     </row>
     <row r="130">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D130">
@@ -5548,22 +5548,22 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>norrbotten_42</t>
+          <t>norrbotten_45</t>
         </is>
       </c>
       <c r="G130">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I130">
-        <v>0.6727272727272724</v>
+        <v>2.192380952380952</v>
       </c>
       <c r="J130">
-        <v>20.85454545454544</v>
+        <v>28.50095238095238</v>
       </c>
     </row>
     <row r="131">
@@ -5572,38 +5572,38 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D131">
         <v>31</v>
       </c>
       <c r="E131">
-        <v>6069</v>
+        <v>6068</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>norrbotten_45</t>
+          <t>norrbotten_46</t>
         </is>
       </c>
       <c r="G131">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I131">
-        <v>0.6727272727272724</v>
+        <v>2.192380952380952</v>
       </c>
       <c r="J131">
-        <v>20.85454545454544</v>
+        <v>28.50095238095238</v>
       </c>
     </row>
     <row r="132">
@@ -5612,38 +5612,38 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D132">
         <v>31</v>
       </c>
       <c r="E132">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>norrbotten_46</t>
+          <t>norrbotten_47</t>
         </is>
       </c>
       <c r="G132">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I132">
-        <v>0.6727272727272724</v>
+        <v>2.192380952380952</v>
       </c>
       <c r="J132">
-        <v>20.85454545454544</v>
+        <v>28.50095238095238</v>
       </c>
     </row>
     <row r="133">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D133">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>norrbotten_47</t>
+          <t>norrbotten_41</t>
         </is>
       </c>
       <c r="G133">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D134">
@@ -5708,22 +5708,22 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>norrbotten_41</t>
+          <t>norrbotten_42</t>
         </is>
       </c>
       <c r="G134">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I134">
-        <v>0.2</v>
+        <v>0.6727272727272724</v>
       </c>
       <c r="J134">
-        <v>2</v>
+        <v>20.85454545454544</v>
       </c>
     </row>
     <row r="135">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>haparanda</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D135">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>norrbotten_42</t>
+          <t>norrbotten_45</t>
         </is>
       </c>
       <c r="G135">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I135">
-        <v>0.2</v>
+        <v>0.6727272727272724</v>
       </c>
       <c r="J135">
-        <v>2</v>
+        <v>20.85454545454544</v>
       </c>
     </row>
     <row r="136">
@@ -5777,33 +5777,33 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D136">
         <v>31</v>
       </c>
       <c r="E136">
-        <v>5966</v>
+        <v>6068</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>norrbotten_43</t>
+          <t>norrbotten_46</t>
         </is>
       </c>
       <c r="G136">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I136">
-        <v>1.419047619047619</v>
+        <v>0.6727272727272724</v>
       </c>
       <c r="J136">
-        <v>41.15238095238094</v>
+        <v>20.85454545454544</v>
       </c>
     </row>
     <row r="137">
@@ -5817,33 +5817,33 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D137">
         <v>31</v>
       </c>
       <c r="E137">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>norrbotten_44</t>
+          <t>norrbotten_47</t>
         </is>
       </c>
       <c r="G137">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I137">
-        <v>1.419047619047619</v>
+        <v>0.6727272727272724</v>
       </c>
       <c r="J137">
-        <v>42.57142857142857</v>
+        <v>20.85454545454544</v>
       </c>
     </row>
     <row r="138">
@@ -5857,33 +5857,33 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D138">
         <v>31</v>
       </c>
       <c r="E138">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>norrbotten_43</t>
+          <t>norrbotten_41</t>
         </is>
       </c>
       <c r="G138">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I138">
-        <v>0.6666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="J138">
-        <v>12.66666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -5897,33 +5897,33 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>lule</t>
+          <t>Haparanda</t>
         </is>
       </c>
       <c r="D139">
         <v>31</v>
       </c>
       <c r="E139">
-        <v>5966</v>
+        <v>6069</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>norrbotten_44</t>
+          <t>norrbotten_42</t>
         </is>
       </c>
       <c r="G139">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I139">
-        <v>0.6666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="J139">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
